--- a/sheets/조재수대금교본/검수/아리랑.xlsx
+++ b/sheets/조재수대금교본/검수/아리랑.xlsx
@@ -3126,8 +3126,7 @@
       <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="G3" s="22"/>
@@ -3139,7 +3138,7 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -3287,8 +3286,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="C6" s="24"/>
@@ -3339,11 +3337,7 @@
         </is>
       </c>
       <c r="S6" s="24"/>
-      <c r="T6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T6" s="21"/>
       <c r="U6" s="24"/>
     </row>
     <row r="7" ht="159.59" customHeight="true">
@@ -3493,17 +3487,9 @@
     </row>
     <row r="10" ht="159.59" customHeight="true">
       <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B10" s="21"/>
       <c r="C10" s="24"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="24"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
@@ -3514,46 +3500,21 @@
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="I10" s="24"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="24"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="24"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N10" s="21"/>
       <c r="O10" s="24"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P10" s="21"/>
       <c r="Q10" s="24"/>
-      <c r="R10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R10" s="21"/>
       <c r="S10" s="24"/>
-      <c r="T10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T10" s="21"/>
       <c r="U10" s="24"/>
     </row>
     <row r="11" ht="6.0" customHeight="true">
@@ -3821,8 +3782,7 @@
       <c r="T20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="U20" s="24"/>

--- a/sheets/조재수대금교본/검수/아리랑.xlsx
+++ b/sheets/조재수대금교본/검수/아리랑.xlsx
@@ -3138,7 +3138,7 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="K3" s="22"/>

--- a/sheets/조재수대금교본/검수/아리랑.xlsx
+++ b/sheets/조재수대금교본/검수/아리랑.xlsx
@@ -3057,32 +3057,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="71.43" customHeight="true">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="159.59" customHeight="true">
+    <row r="3" ht="178.84" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="159.59" customHeight="true">
+    <row r="4" ht="178.84" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="159.59" customHeight="true">
+    <row r="5" ht="178.84" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="23"/>
     </row>
-    <row r="6" ht="159.59" customHeight="true">
+    <row r="6" ht="178.84" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
       <c r="T6" s="21"/>
       <c r="U6" s="24"/>
     </row>
-    <row r="7" ht="159.59" customHeight="true">
+    <row r="7" ht="178.84" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="159.59" customHeight="true">
+    <row r="8" ht="178.84" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="159.59" customHeight="true">
+    <row r="9" ht="178.84" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -3485,7 +3485,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="23"/>
     </row>
-    <row r="10" ht="159.59" customHeight="true">
+    <row r="10" ht="178.84" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -3520,7 +3520,7 @@
     <row r="11" ht="6.0" customHeight="true">
       <c r="A11" s="0"/>
     </row>
-    <row r="12" ht="71.43" customHeight="true">
+    <row r="12" ht="80.0" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="20" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
       <c r="T12" s="20"/>
       <c r="U12" s="20"/>
     </row>
-    <row r="13" ht="159.59" customHeight="true">
+    <row r="13" ht="178.84" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="U13" s="22"/>
     </row>
-    <row r="14" ht="159.59" customHeight="true">
+    <row r="14" ht="178.84" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="23"/>
@@ -3607,7 +3607,7 @@
       <c r="T14" s="21"/>
       <c r="U14" s="23"/>
     </row>
-    <row r="15" ht="159.59" customHeight="true">
+    <row r="15" ht="178.84" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="23"/>
@@ -3635,7 +3635,7 @@
       <c r="T15" s="21"/>
       <c r="U15" s="23"/>
     </row>
-    <row r="16" ht="159.59" customHeight="true">
+    <row r="16" ht="178.84" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="24"/>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="U16" s="24"/>
     </row>
-    <row r="17" ht="159.59" customHeight="true">
+    <row r="17" ht="178.84" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="159.59" customHeight="true">
+    <row r="18" ht="178.84" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -3727,7 +3727,7 @@
       <c r="T18" s="21"/>
       <c r="U18" s="23"/>
     </row>
-    <row r="19" ht="159.59" customHeight="true">
+    <row r="19" ht="178.84" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="23"/>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="U19" s="23"/>
     </row>
-    <row r="20" ht="159.59" customHeight="true">
+    <row r="20" ht="178.84" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="24"/>
@@ -3794,7 +3794,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="10" max="16383" man="1"/>
   </rowBreaks>
